--- a/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
+++ b/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\assignment\term3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F39F093-0FE7-45C6-AA9C-93B70FE0AA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7690A4CA-2EB4-4986-93C0-3E84A2AD4EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1056" windowWidth="11280" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -677,7 +677,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>

--- a/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
+++ b/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\assignment\term3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7690A4CA-2EB4-4986-93C0-3E84A2AD4EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0500B8E6-AD9B-4965-B40D-804FF56C7735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1056" windowWidth="11280" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -721,7 +721,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>

--- a/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
+++ b/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\assignment\term3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0500B8E6-AD9B-4965-B40D-804FF56C7735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1208F627-C22B-4EE5-96AF-E36DB7BC8F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1056" windowWidth="11280" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -737,7 +737,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>

--- a/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
+++ b/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\assignment\term3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1208F627-C22B-4EE5-96AF-E36DB7BC8F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E4F2BC-79EF-4A87-B833-68EDBCC1ACD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1056" windowWidth="11280" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -741,7 +741,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>

--- a/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
+++ b/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\assignment\term3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E4F2BC-79EF-4A87-B833-68EDBCC1ACD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1553E88-601C-4A4C-8AB1-A7BEBF58BE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1056" windowWidth="11280" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -745,7 +745,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>

--- a/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
+++ b/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\assignment\term3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1553E88-601C-4A4C-8AB1-A7BEBF58BE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C8B607-47B7-4BC8-8530-B12FEF674350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1056" windowWidth="11280" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -749,7 +749,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>

--- a/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
+++ b/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\assignment\term3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C8B607-47B7-4BC8-8530-B12FEF674350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBEE8A2-0DEA-4313-9AF7-C12D515469F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1056" windowWidth="11280" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -753,7 +753,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>

--- a/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
+++ b/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\assignment\term3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBEE8A2-0DEA-4313-9AF7-C12D515469F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1EC9EE-E50F-4C6A-BD57-A60A5B253726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1056" windowWidth="11280" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -757,7 +757,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>

--- a/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
+++ b/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\assignment\term3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1EC9EE-E50F-4C6A-BD57-A60A5B253726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13D2A7C-718D-4580-A5A3-668F0D2066E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1056" windowWidth="11280" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -717,7 +717,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
+++ b/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\assignment\term3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13D2A7C-718D-4580-A5A3-668F0D2066E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4532873A-3EB3-43BD-9D5E-BFA5985DCEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1056" windowWidth="11280" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -725,7 +725,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>

--- a/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
+++ b/assignment/term3/18회차_실습체크리스트_김윤지.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jiwab\Desktop\KB 부캠\KB-ITs-Your-Life\assignment\term3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4532873A-3EB3-43BD-9D5E-BFA5985DCEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3185551-F151-4AB5-AEDB-BB67A4ADF089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1056" windowWidth="11280" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1056" windowWidth="13968" windowHeight="11520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -681,15 +681,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
@@ -701,7 +701,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
@@ -709,7 +709,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
@@ -729,11 +729,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -761,7 +761,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" checked="Checked" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
